--- a/DOCX/ChatApp_TestCases.xlsx
+++ b/DOCX/ChatApp_TestCases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021A464F-FADF-4486-B231-9B98985DE190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1EFD552-640E-43F9-9644-617F4D2F61DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$J$12</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="135">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -69,48 +72,6 @@
   </si>
   <si>
     <t>TC001</t>
-  </si>
-  <si>
-    <t>Port = 9999</t>
-  </si>
-  <si>
-    <t>TC002</t>
-  </si>
-  <si>
-    <t>Port = abc</t>
-  </si>
-  <si>
-    <t>TC003</t>
-  </si>
-  <si>
-    <t>TC004</t>
-  </si>
-  <si>
-    <t>TC005</t>
-  </si>
-  <si>
-    <t>TC006</t>
-  </si>
-  <si>
-    <t>TC007</t>
-  </si>
-  <si>
-    <t>TC008</t>
-  </si>
-  <si>
-    <t>TC009</t>
-  </si>
-  <si>
-    <t>TC010</t>
-  </si>
-  <si>
-    <t>TC011</t>
-  </si>
-  <si>
-    <t>IP=127.0.0.1; Port=9999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server </t>
   </si>
   <si>
     <t>Server</t>
@@ -123,10 +84,29 @@
 Chưa có server nào chạy.</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Nhập port hợp lệ vào txtPort (vd: 9999)
+2. Bấm nút Bắt đầu
+3. Quan sát giao diện log và trạng thái các nút </t>
+  </si>
+  <si>
+    <t>Port = 9999</t>
+  </si>
+  <si>
+    <t>Server Log hiện: [HỆ THỐNG] Server khởi động trên cổng 9999; 
+Các nút Bắt đầu, port sẽ ngừng hoạt động ngoài trừ nút Dừng</t>
+  </si>
+  <si>
+    <t>TC002</t>
+  </si>
+  <si>
     <t>Sever</t>
   </si>
   <si>
     <t>[Negative] Khởi động server với port đã bị dùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ứng dụng Server 1 đang mở và chạy thành công trên Port 9999.
+</t>
   </si>
   <si>
     <t>1.Nhập port của Server 1 đã dùng (9999) vào ô txtPort của Server 2.
@@ -141,16 +121,16 @@
     <t>Khi Server 1 hoạt động, khởi chạy Server 2 thì nó vẫn hiện lên trên log Server 2 là bắt đầu hoạt động nhưng nó thực chất không hoạt động.</t>
   </si>
   <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server </t>
+  </si>
+  <si>
     <t>[Negative] khởi động server với port không phải số</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nhập port hợp lệ vào txtPort (vd: 9999)
-2. Bấm nút Bắt đầu
-3. Quan sát giao diện log và trạng thái các nút </t>
-  </si>
-  <si>
-    <t>Server Log hiện: [HỆ THỐNG] Server khởi động trên cổng 9999; 
-Các nút Bắt đầu, port sẽ ngừng hoạt động ngoài trừ nút Dừng</t>
   </si>
   <si>
     <t>1. Nhập giá trị không phải số vào txtPort (vd: 'abc')
@@ -158,10 +138,20 @@
 3. Quan sát thông báo hệ thống</t>
   </si>
   <si>
+    <t>Port = abc</t>
+  </si>
+  <si>
+    <t>Hiện thông báo  'lỗi khởi chạy: ...'; 
+Nhấn ok để tiếp tục, các nút giữ nguyên trạng thái để chờ nhập lại.</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>Server - Cilent</t>
+  </si>
+  <si>
     <t>[Positive] Client gửi lệnh Login và được thêm vào danh sách online</t>
-  </si>
-  <si>
-    <t>Server - Cilent</t>
   </si>
   <si>
     <t xml:space="preserve">Server, Cilent đang chạy
@@ -180,29 +170,25 @@
 Số người online tăng lên 1</t>
   </si>
   <si>
+    <t>TC005</t>
+  </si>
+  <si>
     <t xml:space="preserve">[Negative] Đăng nhập bằng username đã tồn tại. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ứng dụng Server 1 đang mở và chạy thành công trên Port 9999.
-</t>
   </si>
   <si>
     <t>Server đang chạy; 
 Cilent 'huy' đã online à kết nối với server.</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Client 2, nhập đúng username, ip, port và đăng nhập
+2. Quan sát log và số người online </t>
+  </si>
+  <si>
     <t xml:space="preserve"> username (vd: huy)</t>
   </si>
   <si>
     <t>Cilent B hiển thị thông báo : "Tên người dùng đã tồn tại"
 Nhấn ok để tiếp  tục, chờ nhập username mới.</t>
-  </si>
-  <si>
-    <t>Hiện thông báo  'lỗi khởi chạy: ...'; 
-Nhấn ok để tiếp tục, các nút giữ nguyên trạng thái để chờ nhập lại.</t>
-  </si>
-  <si>
-    <t>Fail</t>
   </si>
   <si>
     <t>Cilent B vẫn mở cửa sổ chat bình thường
@@ -210,6 +196,9 @@
 Cilent B vẫn gửi được tin nhắn và hiển thị trên Log Server</t>
   </si>
   <si>
+    <t>TC006</t>
+  </si>
+  <si>
     <t xml:space="preserve">[Negative] Cilent khi server  đột ngột dừng hoạt động </t>
   </si>
   <si>
@@ -233,6 +222,9 @@
 Mọi thao tác bị vô hiệu hóa</t>
   </si>
   <si>
+    <t>TC007</t>
+  </si>
+  <si>
     <t>[Positive] Client ngắt kết nối đột ngột</t>
   </si>
   <si>
@@ -252,24 +244,34 @@
 Bên chat cilent còn lại cũng gửi thông báo tới là: [HỆ THỐNG] tien đã thoát và đồng thời giảm người dúng online xuống còn 1</t>
   </si>
   <si>
+    <t>TC008</t>
+  </si>
+  <si>
     <t>Server-Cilent</t>
+  </si>
+  <si>
+    <t>[Positive] Kết nối tới server với IP/Port hợp lệ</t>
+  </si>
+  <si>
+    <t>Server đang chạy</t>
+  </si>
+  <si>
+    <t>1. Nhập IP hợp lệ vào  txtIP (127.0.0.1)
+2. Nhập Port txtPort (9999)
+3. Bam nút Đăng nhập</t>
+  </si>
+  <si>
+    <t>IP=127.0.0.1; Port=9999</t>
   </si>
   <si>
     <t xml:space="preserve">Kết nối thành công và chuyển tiếp vào phần chat cilent 
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. Client 2, nhập đúng username, ip, port và đăng nhập
-2. Quan sát log và số người online </t>
-  </si>
-  <si>
-    <t>[Positive] Kết nối tới server với IP/Port hợp lệ</t>
+    <t>TC009</t>
   </si>
   <si>
     <t>[Negative] Kết nối tới server với IP/Port sai</t>
-  </si>
-  <si>
-    <t>Server đang chạy</t>
   </si>
   <si>
     <t>1. Nhập IP/Port không tồn tại (vd 10.0.0.1 / 1)
@@ -283,12 +285,10 @@
     <t>Hiện thông báo: "lỗi không thể kết nối,….."</t>
   </si>
   <si>
+    <t>TC010</t>
+  </si>
+  <si>
     <t>[Negative] Đăng nhập bằng username rỗng</t>
-  </si>
-  <si>
-    <t>1. Nhập IP hợp lệ vào  txtIP (127.0.0.1)
-2. Nhập Port txtPort (9999)
-3. Bam nút Đăng nhập</t>
   </si>
   <si>
     <t>1. Để txtUsername rỗng
@@ -302,6 +302,12 @@
     <t>Hiện thông báo: "lỗi: vui lòng nhập tên người dùng"</t>
   </si>
   <si>
+    <t>TC011</t>
+  </si>
+  <si>
+    <t>[Negative] Kiểm tra tính năng gửi ảnh, video</t>
+  </si>
+  <si>
     <t>Sever và cilent đang chạy và liên kết với nhau</t>
   </si>
   <si>
@@ -312,20 +318,190 @@
     <t>Ảnh, video</t>
   </si>
   <si>
-    <t>[Negative] Kiểm tra tính năng gửi ảnh, video</t>
-  </si>
-  <si>
     <t>Hiện ra ảnh hoặc video để xem trước và có thể chủ động nhấn tải để tải ảnh hoặc video về</t>
   </si>
   <si>
     <t>Tự động tải video về máy của cilent mà không được xem trước (không khả thi khi file lớn)</t>
+  </si>
+  <si>
+    <t>TC012</t>
+  </si>
+  <si>
+    <t>[Positive] Gửi tin nhắn văn bản</t>
+  </si>
+  <si>
+    <t>Server và 2 client đang online</t>
+  </si>
+  <si>
+    <t>1. Client A nhập tin nhắn vào ô chat
+2. Bấm nút Gửi
+3. Quan sát màn hình Client B</t>
+  </si>
+  <si>
+    <t>Xin chào mọi người!</t>
+  </si>
+  <si>
+    <t>Client B nhận được tin nhắn, hiển thị đúng username + timestamp</t>
+  </si>
+  <si>
+    <t>TC013</t>
+  </si>
+  <si>
+    <t>[Negative] Gửi tin nhắn rỗng</t>
+  </si>
+  <si>
+    <t>Client đang kết nối server</t>
+  </si>
+  <si>
+    <t>1. Để trống ô tin nhắn
+2. Bấm nút Gửi</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>Hệ thống không gửi, không có gì xảy ra hoặc hiển thị cảnh báo</t>
+  </si>
+  <si>
+    <t>TC014</t>
+  </si>
+  <si>
+    <t>[Positive] Gửi emoji thành công</t>
+  </si>
+  <si>
+    <t>1. Client A chọn emoji từ bảng picker
+2. Bấm Gửi
+3. Quan sát màn hình Client B</t>
+  </si>
+  <si>
+    <t>😂</t>
+  </si>
+  <si>
+    <t>Emoji hiển thị đúng và giống nhau trên tất cả client</t>
+  </si>
+  <si>
+    <t>TC015</t>
+  </si>
+  <si>
+    <t>Online List</t>
+  </si>
+  <si>
+    <t>[Positive] Danh sách online cập nhật khi user mới join</t>
+  </si>
+  <si>
+    <t>Server đang chạy, ít nhất 1 client online</t>
+  </si>
+  <si>
+    <t>1. Client mới đăng nhập thành công
+2. Quan sát danh sách user online trên tất cả client</t>
+  </si>
+  <si>
+    <t>username = "Tien"</t>
+  </si>
+  <si>
+    <t>Tất cả client thấy "Tien" trong danh sách ngay lập tức, số online tăng đúng</t>
+  </si>
+  <si>
+    <t>TC016</t>
+  </si>
+  <si>
+    <t>[Positive] Danh sách online cập nhật khi user rời</t>
+  </si>
+  <si>
+    <t>Server đang chạy, ít nhất 2 client online</t>
+  </si>
+  <si>
+    <t>1. Client A đóng ứng dụng
+2. Quan sát danh sách user online trên Client B</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Client A bị xóa khỏi danh sách của tất cả client, số online giảm đúng</t>
+  </si>
+  <si>
+    <t>TC017</t>
+  </si>
+  <si>
+    <t>Server - Client</t>
+  </si>
+  <si>
+    <t>[Negative] Đăng nhập với username chỉ có khoảng trắng</t>
+  </si>
+  <si>
+    <t>Server đang chạy, client đang mở form đăng nhập</t>
+  </si>
+  <si>
+    <t>1. Nhập " " (toàn khoảng trắng) vào ô username
+2. Bấm nút Đăng nhập</t>
+  </si>
+  <si>
+    <t>username = " "</t>
+  </si>
+  <si>
+    <t>Hệ thống trim và báo lỗi "Username không hợp lệ". Không cho đăng nhập</t>
+  </si>
+  <si>
+    <t>TC018</t>
+  </si>
+  <si>
+    <t>[Positive] Nhiều client kết nối đồng thời</t>
+  </si>
+  <si>
+    <t>Server đang chạy, chưa có client nào</t>
+  </si>
+  <si>
+    <t>1. Mở 5 client cùng lúc
+2. Đăng nhập với username khác nhau
+3. Quan sát server log và danh sách online</t>
+  </si>
+  <si>
+    <t>username: a, b, c, d, e</t>
+  </si>
+  <si>
+    <t>Server xử lý tất cả 5 kết nối, danh sách online hiển thị đúng 5 người</t>
+  </si>
+  <si>
+    <t>TC019</t>
+  </si>
+  <si>
+    <t>[Negative] Gửi tin nhắn rất dài</t>
+  </si>
+  <si>
+    <t>1. Client A nhập tin nhắn dài 1000+ ký tự
+2. Bấm Gửi
+3. Quan sát hiển thị cả 2 phía</t>
+  </si>
+  <si>
+    <t>Chuỗi 1000 ký tự</t>
+  </si>
+  <si>
+    <t>Tin nhắn gửi thành công, hiển thị đầy đủ hoặc wrap text, không bị cắt xén hay crash</t>
+  </si>
+  <si>
+    <t>TC020</t>
+  </si>
+  <si>
+    <t>[Positive] Gửi kết hợp emoji và text</t>
+  </si>
+  <si>
+    <t>1. Client A nhập text kèm emoji
+2. Bấm Gửi
+3. Quan sát Client B</t>
+  </si>
+  <si>
+    <t>"Chúc mừng 🎂🎉 sinh nhật!"</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng thứ tự text và emoji, không vỡ layout</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,6 +524,30 @@
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -376,7 +576,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -399,11 +599,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -433,9 +674,60 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -735,22 +1027,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="49.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="45.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="46.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="44.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -782,307 +1074,514 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="60">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="60">
       <c r="A3" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" spans="1:10" ht="45">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="F4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="G4" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="9"/>
-    </row>
-    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="45">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="10" customFormat="1" ht="60">
       <c r="A6" s="5" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="H6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10" s="10" customFormat="1" ht="60">
+      <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="B7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="E7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" spans="1:10" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="H7" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="I7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" ht="60">
+      <c r="A8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="B8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="D8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="E8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="F8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="45">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>72</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="45.75">
       <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="20" t="s">
         <v>69</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="45.75">
       <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="20" t="s">
         <v>74</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:10" s="10" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="10" customFormat="1" ht="47.25" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="22" t="s">
         <v>80</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>81</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:10" ht="45.75">
+      <c r="A13" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30.75">
+      <c r="A14" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="45.75">
+      <c r="A15" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30.75">
+      <c r="A16" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30.75">
+      <c r="A17" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30.75">
+      <c r="A18" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="45.75">
+      <c r="A19" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="45.75">
+      <c r="A20" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="45.75">
+      <c r="A21" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>134</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/DOCX/ChatApp_TestCases.xlsx
+++ b/DOCX/ChatApp_TestCases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1EFD552-640E-43F9-9644-617F4D2F61DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E265351D-9363-4482-8C21-99A229891FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,11 +18,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$J$12</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="124">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -72,6 +69,48 @@
   </si>
   <si>
     <t>TC001</t>
+  </si>
+  <si>
+    <t>Port = 9999</t>
+  </si>
+  <si>
+    <t>TC002</t>
+  </si>
+  <si>
+    <t>Port = abc</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>TC005</t>
+  </si>
+  <si>
+    <t>TC006</t>
+  </si>
+  <si>
+    <t>TC007</t>
+  </si>
+  <si>
+    <t>TC008</t>
+  </si>
+  <si>
+    <t>TC009</t>
+  </si>
+  <si>
+    <t>TC010</t>
+  </si>
+  <si>
+    <t>TC011</t>
+  </si>
+  <si>
+    <t>IP=127.0.0.1; Port=9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server </t>
   </si>
   <si>
     <t>Server</t>
@@ -82,6 +121,20 @@
   <si>
     <t>Ứng dụng ChatServer đang mở;
 Chưa có server nào chạy.</t>
+  </si>
+  <si>
+    <t>Sever</t>
+  </si>
+  <si>
+    <t>[Negative] Khởi động server với port đã bị dùng</t>
+  </si>
+  <si>
+    <t>1.Nhập port của Server 1 đã dùng (9999) vào ô txtPort của Server 2.
+2.Bấm nút Bắt đầu
+3.Quan sát giao diện Log và trạng thái các nút bấm</t>
+  </si>
+  <si>
+    <t>[Negative] khởi động server với port không phải số</t>
   </si>
   <si>
     <t xml:space="preserve">1. Nhập port hợp lệ vào txtPort (vd: 9999)
@@ -89,48 +142,8 @@
 3. Quan sát giao diện log và trạng thái các nút </t>
   </si>
   <si>
-    <t>Port = 9999</t>
-  </si>
-  <si>
     <t>Server Log hiện: [HỆ THỐNG] Server khởi động trên cổng 9999; 
 Các nút Bắt đầu, port sẽ ngừng hoạt động ngoài trừ nút Dừng</t>
-  </si>
-  <si>
-    <t>TC002</t>
-  </si>
-  <si>
-    <t>Sever</t>
-  </si>
-  <si>
-    <t>[Negative] Khởi động server với port đã bị dùng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ứng dụng Server 1 đang mở và chạy thành công trên Port 9999.
-</t>
-  </si>
-  <si>
-    <t>1.Nhập port của Server 1 đã dùng (9999) vào ô txtPort của Server 2.
-2.Bấm nút Bắt đầu
-3.Quan sát giao diện Log và trạng thái các nút bấm</t>
-  </si>
-  <si>
-    <t>Hệ thống hiển thị  cảnh báo: "Lỗi khởi chạy do port đã sử dụng"
-Các nút giữ nguyên trạng thái đề chở nhập lại.</t>
-  </si>
-  <si>
-    <t>Khi Server 1 hoạt động, khởi chạy Server 2 thì nó vẫn hiện lên trên log Server 2 là bắt đầu hoạt động nhưng nó thực chất không hoạt động.</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>TC003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server </t>
-  </si>
-  <si>
-    <t>[Negative] khởi động server với port không phải số</t>
   </si>
   <si>
     <t>1. Nhập giá trị không phải số vào txtPort (vd: 'abc')
@@ -138,20 +151,10 @@
 3. Quan sát thông báo hệ thống</t>
   </si>
   <si>
-    <t>Port = abc</t>
-  </si>
-  <si>
-    <t>Hiện thông báo  'lỗi khởi chạy: ...'; 
-Nhấn ok để tiếp tục, các nút giữ nguyên trạng thái để chờ nhập lại.</t>
-  </si>
-  <si>
-    <t>TC004</t>
+    <t>[Positive] Client gửi lệnh Login và được thêm vào danh sách online</t>
   </si>
   <si>
     <t>Server - Cilent</t>
-  </si>
-  <si>
-    <t>[Positive] Client gửi lệnh Login và được thêm vào danh sách online</t>
   </si>
   <si>
     <t xml:space="preserve">Server, Cilent đang chạy
@@ -170,25 +173,29 @@
 Số người online tăng lên 1</t>
   </si>
   <si>
-    <t>TC005</t>
-  </si>
-  <si>
     <t xml:space="preserve">[Negative] Đăng nhập bằng username đã tồn tại. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ứng dụng Server 1 đang mở và chạy thành công trên Port 9999.
+</t>
   </si>
   <si>
     <t>Server đang chạy; 
 Cilent 'huy' đã online à kết nối với server.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Client 2, nhập đúng username, ip, port và đăng nhập
-2. Quan sát log và số người online </t>
-  </si>
-  <si>
     <t xml:space="preserve"> username (vd: huy)</t>
   </si>
   <si>
     <t>Cilent B hiển thị thông báo : "Tên người dùng đã tồn tại"
 Nhấn ok để tiếp  tục, chờ nhập username mới.</t>
+  </si>
+  <si>
+    <t>Hiện thông báo  'lỗi khởi chạy: ...'; 
+Nhấn ok để tiếp tục, các nút giữ nguyên trạng thái để chờ nhập lại.</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
   <si>
     <t>Cilent B vẫn mở cửa sổ chat bình thường
@@ -196,9 +203,6 @@
 Cilent B vẫn gửi được tin nhắn và hiển thị trên Log Server</t>
   </si>
   <si>
-    <t>TC006</t>
-  </si>
-  <si>
     <t xml:space="preserve">[Negative] Cilent khi server  đột ngột dừng hoạt động </t>
   </si>
   <si>
@@ -218,13 +222,6 @@
 Hiện thông báo : "Mất kết nối với server" và quay lại trang  Đăng nhập</t>
   </si>
   <si>
-    <t>Chat Cilent không tự đóng, người dùng vẫn kệt ở giao diện chat
-Mọi thao tác bị vô hiệu hóa</t>
-  </si>
-  <si>
-    <t>TC007</t>
-  </si>
-  <si>
     <t>[Positive] Client ngắt kết nối đột ngột</t>
   </si>
   <si>
@@ -244,16 +241,38 @@
 Bên chat cilent còn lại cũng gửi thông báo tới là: [HỆ THỐNG] tien đã thoát và đồng thời giảm người dúng online xuống còn 1</t>
   </si>
   <si>
-    <t>TC008</t>
-  </si>
-  <si>
     <t>Server-Cilent</t>
   </si>
   <si>
+    <t xml:space="preserve">Kết nối thành công và chuyển tiếp vào phần chat cilent 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Client 2, nhập đúng username, ip, port và đăng nhập
+2. Quan sát log và số người online </t>
+  </si>
+  <si>
     <t>[Positive] Kết nối tới server với IP/Port hợp lệ</t>
   </si>
   <si>
+    <t>[Negative] Kết nối tới server với IP/Port sai</t>
+  </si>
+  <si>
     <t>Server đang chạy</t>
+  </si>
+  <si>
+    <t>1. Nhập IP/Port không tồn tại (vd 10.0.0.1 / 1)
+2. Bấm
+3. Quan sát login cilent</t>
+  </si>
+  <si>
+    <t>IP=10.0.0.1; Port=1</t>
+  </si>
+  <si>
+    <t>Hiện thông báo: "lỗi không thể kết nối,….."</t>
+  </si>
+  <si>
+    <t>[Negative] Đăng nhập bằng username rỗng</t>
   </si>
   <si>
     <t>1. Nhập IP hợp lệ vào  txtIP (127.0.0.1)
@@ -261,36 +280,6 @@
 3. Bam nút Đăng nhập</t>
   </si>
   <si>
-    <t>IP=127.0.0.1; Port=9999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kết nối thành công và chuyển tiếp vào phần chat cilent 
-</t>
-  </si>
-  <si>
-    <t>TC009</t>
-  </si>
-  <si>
-    <t>[Negative] Kết nối tới server với IP/Port sai</t>
-  </si>
-  <si>
-    <t>1. Nhập IP/Port không tồn tại (vd 10.0.0.1 / 1)
-2. Bấm
-3. Quan sát login cilent</t>
-  </si>
-  <si>
-    <t>IP=10.0.0.1; Port=1</t>
-  </si>
-  <si>
-    <t>Hiện thông báo: "lỗi không thể kết nối,….."</t>
-  </si>
-  <si>
-    <t>TC010</t>
-  </si>
-  <si>
-    <t>[Negative] Đăng nhập bằng username rỗng</t>
-  </si>
-  <si>
     <t>1. Để txtUsername rỗng
 2. Bấm nút Đăng nhập
 3. Quan sát login cilent</t>
@@ -302,12 +291,6 @@
     <t>Hiện thông báo: "lỗi: vui lòng nhập tên người dùng"</t>
   </si>
   <si>
-    <t>TC011</t>
-  </si>
-  <si>
-    <t>[Negative] Kiểm tra tính năng gửi ảnh, video</t>
-  </si>
-  <si>
     <t>Sever và cilent đang chạy và liên kết với nhau</t>
   </si>
   <si>
@@ -318,10 +301,21 @@
     <t>Ảnh, video</t>
   </si>
   <si>
+    <t>[Negative] Kiểm tra tính năng gửi ảnh, video</t>
+  </si>
+  <si>
     <t>Hiện ra ảnh hoặc video để xem trước và có thể chủ động nhấn tải để tải ảnh hoặc video về</t>
   </si>
   <si>
     <t>Tự động tải video về máy của cilent mà không được xem trước (không khả thi khi file lớn)</t>
+  </si>
+  <si>
+    <t>Hệ thống hiển thị  cảnh báo: "Lỗi khởi chạy:..."
+Các nút giữ nguyên trạng thái đề chở nhập lại.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat Cilent tự động chuyển sang giao diện đăng nhập mà không hiện thông báo
+</t>
   </si>
   <si>
     <t>TC012</t>
@@ -353,31 +347,10 @@
     <t>Client đang kết nối server</t>
   </si>
   <si>
-    <t>1. Để trống ô tin nhắn
-2. Bấm nút Gửi</t>
-  </si>
-  <si>
-    <t>""</t>
-  </si>
-  <si>
     <t>Hệ thống không gửi, không có gì xảy ra hoặc hiển thị cảnh báo</t>
   </si>
   <si>
     <t>TC014</t>
-  </si>
-  <si>
-    <t>[Positive] Gửi emoji thành công</t>
-  </si>
-  <si>
-    <t>1. Client A chọn emoji từ bảng picker
-2. Bấm Gửi
-3. Quan sát màn hình Client B</t>
-  </si>
-  <si>
-    <t>😂</t>
-  </si>
-  <si>
-    <t>Emoji hiển thị đúng và giống nhau trên tất cả client</t>
   </si>
   <si>
     <t>TC015</t>
@@ -396,12 +369,6 @@
 2. Quan sát danh sách user online trên tất cả client</t>
   </si>
   <si>
-    <t>username = "Tien"</t>
-  </si>
-  <si>
-    <t>Tất cả client thấy "Tien" trong danh sách ngay lập tức, số online tăng đúng</t>
-  </si>
-  <si>
     <t>TC016</t>
   </si>
   <si>
@@ -415,9 +382,6 @@
 2. Quan sát danh sách user online trên Client B</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>Client A bị xóa khỏi danh sách của tất cả client, số online giảm đúng</t>
   </si>
   <si>
@@ -438,9 +402,6 @@
   </si>
   <si>
     <t>username = " "</t>
-  </si>
-  <si>
-    <t>Hệ thống trim và báo lỗi "Username không hợp lệ". Không cho đăng nhập</t>
   </si>
   <si>
     <t>TC018</t>
@@ -463,45 +424,43 @@
     <t>Server xử lý tất cả 5 kết nối, danh sách online hiển thị đúng 5 người</t>
   </si>
   <si>
-    <t>TC019</t>
-  </si>
-  <si>
-    <t>[Negative] Gửi tin nhắn rất dài</t>
-  </si>
-  <si>
-    <t>1. Client A nhập tin nhắn dài 1000+ ký tự
-2. Bấm Gửi
-3. Quan sát hiển thị cả 2 phía</t>
-  </si>
-  <si>
-    <t>Chuỗi 1000 ký tự</t>
-  </si>
-  <si>
-    <t>Tin nhắn gửi thành công, hiển thị đầy đủ hoặc wrap text, không bị cắt xén hay crash</t>
-  </si>
-  <si>
-    <t>TC020</t>
-  </si>
-  <si>
-    <t>[Positive] Gửi kết hợp emoji và text</t>
-  </si>
-  <si>
-    <t>1. Client A nhập text kèm emoji
-2. Bấm Gửi
-3. Quan sát Client B</t>
-  </si>
-  <si>
-    <t>"Chúc mừng 🎂🎉 sinh nhật!"</t>
-  </si>
-  <si>
-    <t>Hiển thị đúng thứ tự text và emoji, không vỡ layout</t>
+    <t>username = "Tien" ,"Huy"</t>
+  </si>
+  <si>
+    <t>Tất cả client thấy "Tien" và "Huy" trong danh sách ngay lập tức, số online tăng đúng</t>
+  </si>
+  <si>
+    <t>1. Để trống ô tin nhắn hoặc thêm nhiều khoảng cách trắng
+2. Bấm nút Gửi</t>
+  </si>
+  <si>
+    <t>Hệ thống trim và báo lỗi "Vui lòng nhập tên" lại. Không cho đăng nhập</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Client - Đăng nhập</t>
+  </si>
+  <si>
+    <t>Kiểm tra đăng nhập khi Server chưa bật</t>
+  </si>
+  <si>
+    <t>1. Nhập đầy đủ thông tin hợp lệ
+2. Bấm Đăng nhập</t>
+  </si>
+  <si>
+    <t>Server chưa chạy</t>
+  </si>
+  <si>
+    <t>Hiện thống báo lỗi: "không thể kết nối….."</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,31 +486,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
+      <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -575,8 +515,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -601,50 +559,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFD3D3D3"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFD3D3D3"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFD3D3D3"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFD3D3D3"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -658,14 +590,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -674,62 +600,630 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="42">
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C6500"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF006100"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF9C0006"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1027,22 +1521,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="49.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="3" max="3" width="53.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="79.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="44.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.95" customHeight="1">
+    <row r="1" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1074,518 +1568,664 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="G2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:10" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="B3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="G4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="J4" s="7"/>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="J5" s="7"/>
+    </row>
+    <row r="6" spans="1:10" s="8" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="9"/>
+      <c r="B6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="7"/>
     </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" ht="60">
-      <c r="A3" s="5" t="s">
+    <row r="7" spans="1:10" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="9"/>
-    </row>
-    <row r="4" spans="1:10" ht="45">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="9"/>
-    </row>
-    <row r="5" spans="1:10" ht="45">
-      <c r="A5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:10" s="10" customFormat="1" ht="60">
-      <c r="A6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" spans="1:10" s="10" customFormat="1" ht="60">
-      <c r="A7" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" spans="1:10" ht="60">
-      <c r="A8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:10" ht="45">
-      <c r="A9" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="H9" s="4"/>
+      <c r="I9" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="9"/>
+      <c r="E10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="J10" s="7"/>
     </row>
-    <row r="10" spans="1:10" ht="45.75">
-      <c r="A10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="19" t="s">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="20" t="s">
+      <c r="C11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="9"/>
+      <c r="D11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="45.75">
-      <c r="A11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="19" t="s">
+    <row r="12" spans="1:10" s="8" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="20" t="s">
+      <c r="C12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="E12" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="9"/>
+      <c r="F12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="7"/>
     </row>
-    <row r="12" spans="1:10" s="10" customFormat="1" ht="47.25" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="21" t="s">
+    <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="9"/>
+      <c r="C13" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="16" t="s">
+        <v>118</v>
+      </c>
     </row>
-    <row r="13" spans="1:10" ht="45.75">
-      <c r="A13" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="11" t="s">
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>87</v>
+      <c r="C14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="16" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30.75">
-      <c r="A14" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="14" t="s">
+    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H15" s="14"/>
+      <c r="I15" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="14"/>
+      <c r="I16" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="H17" s="14"/>
+      <c r="I17" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>93</v>
+      <c r="C18" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="14"/>
+      <c r="I18" s="16" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="45.75">
-      <c r="A15" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="30.75">
-      <c r="A16" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30.75">
-      <c r="A17" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="13" t="s">
+    <row r="19" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="30.75">
-      <c r="A18" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="G18" s="13" t="s">
+      <c r="B19" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="I19" s="16" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="45.75">
-      <c r="A19" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="45.75">
-      <c r="A20" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="45.75">
-      <c r="A21" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="I2">
+    <cfRule type="cellIs" dxfId="41" priority="40" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="41" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="42" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="cellIs" dxfId="38" priority="37" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="38" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="39" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="cellIs" dxfId="35" priority="34" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="35" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="36" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="cellIs" dxfId="32" priority="31" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="32" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="33" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8">
+    <cfRule type="cellIs" dxfId="29" priority="28" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="29" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="30" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9">
+    <cfRule type="cellIs" dxfId="26" priority="25" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="26" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="27" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11">
+    <cfRule type="cellIs" dxfId="23" priority="22" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="23" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="24" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10">
+    <cfRule type="cellIs" dxfId="20" priority="19" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="20" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="21" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
+    <cfRule type="cellIs" dxfId="17" priority="16" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="18" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I14">
+    <cfRule type="cellIs" dxfId="14" priority="13" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="15" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I17">
+    <cfRule type="cellIs" dxfId="11" priority="10" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="12" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16">
+    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
+    <cfRule type="cellIs" dxfId="5" priority="4" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I18:I19">
+    <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" errorTitle="Lỗi nhập liệu" error="Giá trị nhập không hợp lệ" promptTitle="Trạng thái" prompt="Chọn trạng thái kiểm thử" sqref="I2:I5 I8:I11 I13:I19" xr:uid="{F4E13127-AF70-4FC7-8C3A-C19B29911721}">
+      <formula1>"Pass,Fail,Blocked,Untested"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>